--- a/results/01_pollution_assessment/PCA_Stressors/tables/pc_loadings.xlsx
+++ b/results/01_pollution_assessment/PCA_Stressors/tables/pc_loadings.xlsx
@@ -462,19 +462,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8702291985393624</v>
+        <v>0.8426098332337656</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2379641446746292</v>
+        <v>-0.2313546526734319</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.07105278801769738</v>
+        <v>0.2411518425787669</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1827130022512433</v>
+        <v>0.1026503759361502</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1581838477524132</v>
+        <v>-0.1682852949327324</v>
       </c>
     </row>
     <row r="3">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7516662796993644</v>
+        <v>0.7382916875073846</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4159269540841169</v>
+        <v>-0.07356529282836903</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.009669201241349188</v>
+        <v>0.418894115879642</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3428887083211319</v>
+        <v>0.2836296777047332</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1669763089373493</v>
+        <v>-0.2158979053282337</v>
       </c>
     </row>
     <row r="4">
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7037991818052765</v>
+        <v>0.7856936769193553</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1342316645090597</v>
+        <v>0.03185974399667357</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2738314766945599</v>
+        <v>-0.03246341236238463</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5031894760773989</v>
+        <v>-0.4861268731516769</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.04290576823452369</v>
+        <v>-0.003289930666472334</v>
       </c>
     </row>
     <row r="5">
@@ -528,19 +528,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5151483306417299</v>
+        <v>0.753797609479702</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7317658414115079</v>
+        <v>0.4630186191902775</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1921967033167705</v>
+        <v>0.2050017283072944</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01971383312066507</v>
+        <v>0.08621382715040704</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02147117793593797</v>
+        <v>0.1099073078149939</v>
       </c>
     </row>
     <row r="6">
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5849815933099674</v>
+        <v>0.6475091821716934</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2288326968670686</v>
+        <v>0.005629516996371852</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1253045030851519</v>
+        <v>0.1976467661035267</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2110975536903878</v>
+        <v>0.03686022965758368</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.02605531144045951</v>
+        <v>-0.09082019109573224</v>
       </c>
     </row>
     <row r="7">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9236859568955842</v>
+        <v>0.9322203955448971</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05851055499934814</v>
+        <v>0.01680211425625659</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1303087435244772</v>
+        <v>-0.08949768080802946</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1397499600016423</v>
+        <v>-0.1885599715089485</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2077635501025502</v>
+        <v>-0.135052676992677</v>
       </c>
     </row>
     <row r="8">
@@ -594,19 +594,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8508569920196865</v>
+        <v>0.8754218017147287</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1002996207337038</v>
+        <v>-0.03070589622238422</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1394899566632955</v>
+        <v>-0.1051322092809642</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1404083500871058</v>
+        <v>-0.2103175409375931</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.258034181786378</v>
+        <v>-0.1450368809118397</v>
       </c>
     </row>
     <row r="9">
@@ -616,19 +616,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7568136738017586</v>
+        <v>0.2502919797391553</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.475517059753405</v>
+        <v>-0.8766935505360641</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06445292489375971</v>
+        <v>-0.07176467621948833</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4162016518169434</v>
+        <v>0.3195505262903293</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03772586532141763</v>
+        <v>-0.09575163086866406</v>
       </c>
     </row>
     <row r="10">
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1492387911722579</v>
+        <v>0.5349353126741327</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2206785018871727</v>
+        <v>0.5706896341286096</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8421663524838221</v>
+        <v>-0.4514040070533994</v>
       </c>
       <c r="E10" t="n">
-        <v>0.391581521956009</v>
+        <v>0.09577626457236205</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07670048978478905</v>
+        <v>0.3066848026366266</v>
       </c>
     </row>
     <row r="11">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.5552484960147785</v>
+        <v>0.1430457515199384</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6671581283034471</v>
+        <v>0.9134653256305914</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0813582673073638</v>
+        <v>0.06042564881849469</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4501981861406558</v>
+        <v>-0.3243725374214987</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08022077880775023</v>
+        <v>0.07933049319085572</v>
       </c>
     </row>
     <row r="12">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7161461618296157</v>
+        <v>0.1804382946331078</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.3676552722118935</v>
+        <v>-0.8456555511494964</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2155960307069405</v>
+        <v>-0.1131501851156124</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3797318632058666</v>
+        <v>-0.3263044318369706</v>
       </c>
       <c r="F12" t="n">
-        <v>0.191464099829989</v>
+        <v>0.1227562531091653</v>
       </c>
     </row>
     <row r="13">
@@ -704,19 +704,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7956417771140938</v>
+        <v>0.7718381700712107</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2105025932620872</v>
+        <v>-0.06334416499887927</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2935612617016572</v>
+        <v>-0.3794475192338239</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2001884790675518</v>
+        <v>-0.03724642234722</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06886790650655654</v>
+        <v>0.1525657930225801</v>
       </c>
     </row>
     <row r="14">
@@ -726,19 +726,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1622513922330454</v>
+        <v>-0.04318525949826937</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2444577607301594</v>
+        <v>-0.3763553018522882</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1962156393246558</v>
+        <v>0.461930833059982</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01458086909026485</v>
+        <v>-0.1422072184826789</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8372685141895162</v>
+        <v>0.7105098855029567</v>
       </c>
     </row>
     <row r="15">
@@ -748,19 +748,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6540105406045499</v>
+        <v>0.1889271442823267</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.3578965853786691</v>
+        <v>-0.8086734428519774</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2471796404340765</v>
+        <v>-0.06144311211692222</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2808305309241664</v>
+        <v>-0.2985229482334417</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1779647265487449</v>
+        <v>0.06501716786215386</v>
       </c>
     </row>
     <row r="16">
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5114263489382381</v>
+        <v>0.5464825341234987</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.2072619187901369</v>
+        <v>-0.120807380246726</v>
       </c>
       <c r="D16" t="n">
-        <v>0.770708187586743</v>
+        <v>-0.4673205520185378</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.07578910028212038</v>
+        <v>0.5545461960885655</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1099886831713247</v>
+        <v>0.2923633488578299</v>
       </c>
     </row>
     <row r="17">
@@ -792,19 +792,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3541510935229762</v>
+        <v>0.4831822817843334</v>
       </c>
       <c r="C17" t="n">
-        <v>0.463517538084968</v>
+        <v>0.1454497949332251</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.06864382451046237</v>
+        <v>0.5319329090634686</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3509417745051812</v>
+        <v>0.221678616807064</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3503087775069246</v>
+        <v>0.2067329434699587</v>
       </c>
     </row>
     <row r="18">
@@ -822,19 +822,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.892655394744991</v>
+        <v>6.062480474558468</v>
       </c>
       <c r="C19" t="n">
-        <v>2.194022211947241</v>
+        <v>3.754784019181623</v>
       </c>
       <c r="D19" t="n">
-        <v>1.720183089762909</v>
+        <v>1.42267979195643</v>
       </c>
       <c r="E19" t="n">
-        <v>1.409844255664912</v>
+        <v>1.206248851270367</v>
       </c>
       <c r="F19" t="n">
-        <v>1.088277973084644</v>
+        <v>0.9196745716643834</v>
       </c>
     </row>
     <row r="20">
@@ -844,19 +844,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4307909621715619</v>
+        <v>0.3789050296599041</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1371263882467026</v>
+        <v>0.2346740011988513</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1075114431101818</v>
+        <v>0.08891748699727685</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08811526597905699</v>
+        <v>0.07539055320439793</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06801737331779023</v>
+        <v>0.05747966072902393</v>
       </c>
     </row>
     <row r="21">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4307909621715619</v>
+        <v>0.3789050296599041</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5679173504182645</v>
+        <v>0.6135790308587554</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6754287935284463</v>
+        <v>0.7024965178560323</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7635440595075033</v>
+        <v>0.7778870710604302</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8315614328252935</v>
+        <v>0.8353667317894541</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/PCA_Stressors/tables/pc_loadings.xlsx
+++ b/results/01_pollution_assessment/PCA_Stressors/tables/pc_loadings.xlsx
@@ -462,19 +462,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8426098332337656</v>
+        <v>0.5522529762857251</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2313546526734319</v>
+        <v>0.2614621077222274</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2411518425787669</v>
+        <v>0.6847025280818947</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1026503759361502</v>
+        <v>0.1348745596322221</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1682852949327324</v>
+        <v>-0.01315580999896636</v>
       </c>
     </row>
     <row r="3">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7382916875073846</v>
+        <v>0.3286021718193758</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.07356529282836903</v>
+        <v>0.1155970657905251</v>
       </c>
       <c r="D3" t="n">
-        <v>0.418894115879642</v>
+        <v>0.8496043819454753</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2836296777047332</v>
+        <v>0.08513920915411161</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2158979053282337</v>
+        <v>-0.05097144661368676</v>
       </c>
     </row>
     <row r="4">
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7856936769193553</v>
+        <v>0.9013063211742862</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03185974399667357</v>
+        <v>-0.07009863249300835</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.03246341236238463</v>
+        <v>0.1637972703362319</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4861268731516769</v>
+        <v>0.05299456127437974</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.003289930666472334</v>
+        <v>0.09385498742441552</v>
       </c>
     </row>
     <row r="5">
@@ -528,19 +528,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.753797609479702</v>
+        <v>0.4532719293756662</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4630186191902775</v>
+        <v>-0.4516917276918193</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2050017283072944</v>
+        <v>0.5762610153114258</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08621382715040704</v>
+        <v>0.311525188664049</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1099073078149939</v>
+        <v>0.0743617302188188</v>
       </c>
     </row>
     <row r="6">
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6475091821716934</v>
+        <v>0.4389125388860033</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005629516996371852</v>
+        <v>0.009913823447933741</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1976467661035267</v>
+        <v>0.5129970086896134</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03686022965758368</v>
+        <v>0.109819881202097</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.09082019109573224</v>
+        <v>0.001490748831305209</v>
       </c>
     </row>
     <row r="7">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9322203955448971</v>
+        <v>0.8487449663621002</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01680211425625659</v>
+        <v>0.01537367738011247</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08949768080802946</v>
+        <v>0.3748272916603619</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1885599715089485</v>
+        <v>0.2416706860766523</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.135052676992677</v>
+        <v>-0.1077799296637961</v>
       </c>
     </row>
     <row r="8">
@@ -594,19 +594,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8754218017147287</v>
+        <v>0.8247295092999596</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.03070589622238422</v>
+        <v>0.05976639289003855</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1051322092809642</v>
+        <v>0.3237131220773849</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2103175409375931</v>
+        <v>0.2079178074063998</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1450368809118397</v>
+        <v>-0.1088914321158411</v>
       </c>
     </row>
     <row r="9">
@@ -616,19 +616,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2502919797391553</v>
+        <v>0.03911780477122862</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.8766935505360641</v>
+        <v>0.9283047815757686</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.07176467621948833</v>
+        <v>0.2290156117784838</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3195505262903293</v>
+        <v>0.1783190666671801</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.09575163086866406</v>
+        <v>-0.01195529049076407</v>
       </c>
     </row>
     <row r="10">
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5349353126741327</v>
+        <v>0.3756312886592142</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5706896341286096</v>
+        <v>-0.5115218830361011</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4514040070533994</v>
+        <v>-0.004343146726734451</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09577626457236205</v>
+        <v>0.7154710411480663</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3066848026366266</v>
+        <v>-0.06454076514589488</v>
       </c>
     </row>
     <row r="11">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1430457515199384</v>
+        <v>0.2628843809277066</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9134653256305914</v>
+        <v>-0.9483676166137424</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06042564881849469</v>
+        <v>-0.0238156774475415</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3243725374214987</v>
+        <v>-0.02914131807988636</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07933049319085572</v>
+        <v>-0.01083422754592941</v>
       </c>
     </row>
     <row r="12">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1804382946331078</v>
+        <v>0.3757804462960011</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.8456555511494964</v>
+        <v>0.7804618912757526</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1131501851156124</v>
+        <v>-0.1921853801327217</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3263044318369706</v>
+        <v>-0.0727814670945366</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1227562531091653</v>
+        <v>0.2991218210433218</v>
       </c>
     </row>
     <row r="13">
@@ -704,19 +704,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7718381700712107</v>
+        <v>0.6598028645021786</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.06334416499887927</v>
+        <v>0.1063527587419506</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3794475192338239</v>
+        <v>0.1120729135704511</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.03724642234722</v>
+        <v>0.5559866125718882</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1525657930225801</v>
+        <v>-0.007648557813353309</v>
       </c>
     </row>
     <row r="14">
@@ -726,19 +726,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04318525949826937</v>
+        <v>-0.07933856946795569</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.3763553018522882</v>
+        <v>0.1998212665028329</v>
       </c>
       <c r="D14" t="n">
-        <v>0.461930833059982</v>
+        <v>0.06000869450790279</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1422072184826789</v>
+        <v>-0.07149079572561676</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7105098855029567</v>
+        <v>0.9093956456601892</v>
       </c>
     </row>
     <row r="15">
@@ -748,19 +748,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1889271442823267</v>
+        <v>0.3599536832345192</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.8086734428519774</v>
+        <v>0.7501044090334325</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.06144311211692222</v>
+        <v>-0.1272996834497811</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2985229482334417</v>
+        <v>-0.1072531558084863</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06501716786215386</v>
+        <v>0.2585206266884261</v>
       </c>
     </row>
     <row r="16">
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5464825341234987</v>
+        <v>0.1242353963875975</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.120807380246726</v>
+        <v>0.2313849258568814</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4673205520185378</v>
+        <v>0.1925271559578978</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5545461960885655</v>
+        <v>0.9031829773289947</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2923633488578299</v>
+        <v>-0.05333178196170925</v>
       </c>
     </row>
     <row r="17">
@@ -792,19 +792,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4831822817843334</v>
+        <v>0.1082935904848655</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1454497949332251</v>
+        <v>-0.182470355741206</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5319329090634686</v>
+        <v>0.6829164911949409</v>
       </c>
       <c r="E17" t="n">
-        <v>0.221678616807064</v>
+        <v>0.1062698961116354</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2067329434699587</v>
+        <v>0.3267447656143717</v>
       </c>
     </row>
     <row r="18">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.062480474558468</v>
+        <v>6.062480474558465</v>
       </c>
       <c r="C19" t="n">
-        <v>3.754784019181623</v>
+        <v>3.754784019181622</v>
       </c>
       <c r="D19" t="n">
         <v>1.42267979195643</v>
@@ -834,7 +834,7 @@
         <v>1.206248851270367</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9196745716643834</v>
+        <v>0.919674571664383</v>
       </c>
     </row>
     <row r="20">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3789050296599041</v>
+        <v>0.378905029659904</v>
       </c>
       <c r="C20" t="n">
         <v>0.2346740011988513</v>
       </c>
       <c r="D20" t="n">
-        <v>0.08891748699727685</v>
+        <v>0.08891748699727689</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07539055320439793</v>
+        <v>0.07539055320439794</v>
       </c>
       <c r="F20" t="n">
         <v>0.05747966072902393</v>
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3789050296599041</v>
+        <v>0.378905029659904</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6135790308587554</v>
+        <v>0.6135790308587553</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7024965178560323</v>
+        <v>0.7024965178560322</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7778870710604302</v>
+        <v>0.7778870710604301</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8353667317894541</v>
+        <v>0.835366731789454</v>
       </c>
     </row>
   </sheetData>
